--- a/Sessions/2nd October session 1.xlsx
+++ b/Sessions/2nd October session 1.xlsx
@@ -511,21 +511,9 @@
           <t>null 1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>attend</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[20:30:04]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[20:30:04] Completed Exam &amp; Homework at center.</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>excel_import</t>
@@ -560,16 +548,8 @@
           <t>null 2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>attend</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[20:30:05]</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
